--- a/artfynd/A 29588-2025 artfynd.xlsx
+++ b/artfynd/A 29588-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74906999</v>
       </c>
       <c r="B2" t="n">
-        <v>100146</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533918.8603878758</v>
+        <v>533919</v>
       </c>
       <c r="R2" t="n">
-        <v>6330461.133172809</v>
+        <v>6330461</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1985-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 29588-2025 artfynd.xlsx
+++ b/artfynd/A 29588-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74906999</v>
       </c>
       <c r="B2" t="n">
-        <v>102454</v>
+        <v>102460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29588-2025 artfynd.xlsx
+++ b/artfynd/A 29588-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74906999</v>
       </c>
       <c r="B2" t="n">
-        <v>102460</v>
+        <v>102461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29588-2025 artfynd.xlsx
+++ b/artfynd/A 29588-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74906999</v>
       </c>
       <c r="B2" t="n">
-        <v>102461</v>
+        <v>102488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29588-2025 artfynd.xlsx
+++ b/artfynd/A 29588-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74906999</v>
       </c>
       <c r="B2" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29588-2025 artfynd.xlsx
+++ b/artfynd/A 29588-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74906999</v>
       </c>
       <c r="B2" t="n">
-        <v>102494</v>
+        <v>102501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29588-2025 artfynd.xlsx
+++ b/artfynd/A 29588-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74906999</v>
       </c>
       <c r="B2" t="n">
-        <v>102501</v>
+        <v>102505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29588-2025 artfynd.xlsx
+++ b/artfynd/A 29588-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74906999</v>
       </c>
       <c r="B2" t="n">
-        <v>102505</v>
+        <v>102512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29588-2025 artfynd.xlsx
+++ b/artfynd/A 29588-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74906999</v>
       </c>
       <c r="B2" t="n">
-        <v>102515</v>
+        <v>102520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29588-2025 artfynd.xlsx
+++ b/artfynd/A 29588-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74906999</v>
       </c>
       <c r="B2" t="n">
-        <v>102520</v>
+        <v>102528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29588-2025 artfynd.xlsx
+++ b/artfynd/A 29588-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74906999</v>
       </c>
       <c r="B2" t="n">
-        <v>102528</v>
+        <v>102538</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
